--- a/ClosedXML.Tests/Resource/Examples/Ranges/Sorting.xlsx
+++ b/ClosedXML.Tests/Resource/Examples/Ranges/Sorting.xlsx
@@ -1633,33 +1633,33 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:1">
-      <x:c r="A1" s="9" t="n">
+      <x:c r="A1" s="9">
         <x:v>0.378125</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:1">
-      <x:c r="A2" s="10" t="n">
+      <x:c r="A2" s="10">
         <x:v>1.05034722222222</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:1">
-      <x:c r="A3" s="5" t="n">
+      <x:c r="A3" s="5">
         <x:v>1.15</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:1">
-      <x:c r="A4" s="11">
+      <x:c r="A4" s="4">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:1">
+      <x:c r="A5" s="11">
         <x:v>40573</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" spans="1:1">
-      <x:c r="A5" s="12">
+    <x:row r="6" spans="1:1">
+      <x:c r="A6" s="12">
         <x:v>40648</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:1">
-      <x:c r="A6" s="4" t="n">
-        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:1">
@@ -1686,32 +1686,32 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:1">
-      <x:c r="A1" s="5" t="n">
+      <x:c r="A1" s="5">
         <x:v>1.15</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:1">
-      <x:c r="A2" s="8" t="n">
+      <x:c r="A2" s="8">
         <x:v>1.3</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:1">
-      <x:c r="A3" s="6" t="n">
+      <x:c r="A3" s="6">
         <x:v>4.15</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:1">
-      <x:c r="A4" s="2" t="n">
+      <x:c r="A4" s="2">
         <x:v>4.3</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:1">
-      <x:c r="A5" s="4" t="n">
+      <x:c r="A5" s="4">
         <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:1">
-      <x:c r="A6" s="1" t="n">
+      <x:c r="A6" s="1">
         <x:v>1230</x:v>
       </x:c>
     </x:row>
@@ -1739,32 +1739,32 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:1">
-      <x:c r="A1" s="13" t="n">
+      <x:c r="A1" s="13">
         <x:v>0.00850694444444444</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:1">
-      <x:c r="A2" s="14" t="n">
+      <x:c r="A2" s="14">
         <x:v>0.0446180555555556</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:1">
-      <x:c r="A3" s="9" t="n">
+      <x:c r="A3" s="9">
         <x:v>0.0447916666666667</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:1">
-      <x:c r="A4" s="15" t="n">
+      <x:c r="A4" s="15">
         <x:v>0.524548611111111</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:1">
-      <x:c r="A5" s="10" t="n">
+      <x:c r="A5" s="10">
         <x:v>1.05034722222222</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:1">
-      <x:c r="A6" s="16" t="n">
+      <x:c r="A6" s="16">
         <x:v>1.87586805555556</x:v>
       </x:c>
     </x:row>

--- a/ClosedXML.Tests/Resource/Examples/Ranges/Sorting.xlsx
+++ b/ClosedXML.Tests/Resource/Examples/Ranges/Sorting.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:si>
     <x:t>Column1</x:t>
   </x:si>
@@ -582,7 +582,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
@@ -693,7 +693,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
@@ -746,7 +746,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
@@ -799,7 +799,7 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
@@ -896,7 +896,7 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
@@ -949,7 +949,7 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
@@ -1002,7 +1002,7 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
@@ -1099,7 +1099,7 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
@@ -1196,7 +1196,7 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
@@ -1293,7 +1293,7 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
@@ -1346,7 +1346,7 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
@@ -1399,7 +1399,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
@@ -1510,7 +1510,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
@@ -1545,7 +1545,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
@@ -1625,7 +1625,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
@@ -1678,7 +1678,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
@@ -1731,7 +1731,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
@@ -1784,7 +1784,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
@@ -1837,7 +1837,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>

--- a/ClosedXML.Tests/Resource/Examples/Ranges/Sorting.xlsx
+++ b/ClosedXML.Tests/Resource/Examples/Ranges/Sorting.xlsx
@@ -6,25 +6,25 @@
     <x:workbookView firstSheet="0" activeTab="0"/>
   </x:bookViews>
   <x:sheets>
-    <x:sheet name="Table" sheetId="2" r:id="rId2"/>
-    <x:sheet name="Table2" sheetId="3" r:id="rId3"/>
-    <x:sheet name="Rows" sheetId="4" r:id="rId4"/>
-    <x:sheet name="Columns" sheetId="5" r:id="rId5"/>
-    <x:sheet name="Mixed" sheetId="6" r:id="rId6"/>
-    <x:sheet name="Numbers" sheetId="7" r:id="rId7"/>
-    <x:sheet name="TimeSpans" sheetId="8" r:id="rId8"/>
-    <x:sheet name="Dates" sheetId="9" r:id="rId9"/>
-    <x:sheet name="Include Blanks" sheetId="10" r:id="rId10"/>
-    <x:sheet name="Include Blanks Column" sheetId="11" r:id="rId11"/>
-    <x:sheet name="Include Blanks Column Desc" sheetId="12" r:id="rId12"/>
-    <x:sheet name="Case Sensitive" sheetId="13" r:id="rId13"/>
-    <x:sheet name="Case Sensitive Column" sheetId="14" r:id="rId14"/>
-    <x:sheet name="Case Sensitive Column Desc" sheetId="15" r:id="rId15"/>
-    <x:sheet name="Simple" sheetId="16" r:id="rId16"/>
-    <x:sheet name="Simple Desc" sheetId="17" r:id="rId17"/>
-    <x:sheet name="Simple Columns" sheetId="18" r:id="rId18"/>
-    <x:sheet name="Simple Column" sheetId="19" r:id="rId19"/>
-    <x:sheet name="Simple Column Desc" sheetId="20" r:id="rId20"/>
+    <x:sheet name="Table" sheetId="1" r:id="rId2"/>
+    <x:sheet name="Table2" sheetId="2" r:id="rId3"/>
+    <x:sheet name="Rows" sheetId="3" r:id="rId4"/>
+    <x:sheet name="Columns" sheetId="4" r:id="rId5"/>
+    <x:sheet name="Mixed" sheetId="5" r:id="rId6"/>
+    <x:sheet name="Numbers" sheetId="6" r:id="rId7"/>
+    <x:sheet name="TimeSpans" sheetId="7" r:id="rId8"/>
+    <x:sheet name="Dates" sheetId="8" r:id="rId9"/>
+    <x:sheet name="Include Blanks" sheetId="9" r:id="rId10"/>
+    <x:sheet name="Include Blanks Column" sheetId="10" r:id="rId11"/>
+    <x:sheet name="Include Blanks Column Desc" sheetId="11" r:id="rId12"/>
+    <x:sheet name="Case Sensitive" sheetId="12" r:id="rId13"/>
+    <x:sheet name="Case Sensitive Column" sheetId="13" r:id="rId14"/>
+    <x:sheet name="Case Sensitive Column Desc" sheetId="14" r:id="rId15"/>
+    <x:sheet name="Simple" sheetId="15" r:id="rId16"/>
+    <x:sheet name="Simple Desc" sheetId="16" r:id="rId17"/>
+    <x:sheet name="Simple Columns" sheetId="17" r:id="rId18"/>
+    <x:sheet name="Simple Column" sheetId="18" r:id="rId19"/>
+    <x:sheet name="Simple Column Desc" sheetId="19" r:id="rId20"/>
   </x:sheets>
   <x:definedNames/>
   <x:calcPr calcId="125725"/>

--- a/ClosedXML.Tests/Resource/Examples/Ranges/Sorting.xlsx
+++ b/ClosedXML.Tests/Resource/Examples/Ranges/Sorting.xlsx
@@ -88,12 +88,12 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFCD5C5C"/>
+        <x:fgColor rgb="FFA9A9A9"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFA9A9A9"/>
+        <x:fgColor rgb="FFCD5C5C"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -169,7 +169,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="46" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="46" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="46" fontId="0" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -196,7 +196,7 @@
     <x:xf numFmtId="14" fontId="0" fillId="6" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="14" fontId="0" fillId="5" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -243,7 +243,7 @@
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="46" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="46" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -279,7 +279,7 @@
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="14" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -616,24 +616,24 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
@@ -654,7 +654,7 @@
       <x:c r="B6" s="5" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C6" s="5" t="s"/>
+      <x:c r="C6" s="5"/>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="6" t="s">
@@ -663,10 +663,10 @@
       <x:c r="B7" s="6" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="s"/>
+      <x:c r="C7" s="6"/>
     </x:row>
     <x:row r="8" spans="1:3">
-      <x:c r="A8" s="7" t="s"/>
+      <x:c r="A8" s="7"/>
       <x:c r="B8" s="7" t="s">
         <x:v>3</x:v>
       </x:c>
@@ -678,7 +678,7 @@
       <x:c r="A9" s="8" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B9" s="8" t="s"/>
+      <x:c r="B9" s="8"/>
       <x:c r="C9" s="8" t="s">
         <x:v>5</x:v>
       </x:c>
@@ -701,10 +701,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:1">
-      <x:c r="A1" s="7" t="s"/>
+      <x:c r="A1" s="2"/>
     </x:row>
     <x:row r="2" spans="1:1">
-      <x:c r="A2" s="3" t="s"/>
+      <x:c r="A2" s="7"/>
     </x:row>
     <x:row r="3" spans="1:1">
       <x:c r="A3" s="1" t="s">
@@ -727,7 +727,7 @@
       </x:c>
     </x:row>
     <x:row r="7" spans="1:1">
-      <x:c r="A7" s="2" t="s">
+      <x:c r="A7" s="3" t="s">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -764,7 +764,7 @@
       </x:c>
     </x:row>
     <x:row r="3" spans="1:1">
-      <x:c r="A3" s="2" t="s">
+      <x:c r="A3" s="3" t="s">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -784,10 +784,10 @@
       </x:c>
     </x:row>
     <x:row r="7" spans="1:1">
-      <x:c r="A7" s="7" t="s"/>
+      <x:c r="A7" s="2"/>
     </x:row>
     <x:row r="8" spans="1:1">
-      <x:c r="A8" s="3" t="s"/>
+      <x:c r="A8" s="7"/>
     </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
@@ -818,36 +818,36 @@
       </x:c>
     </x:row>
     <x:row r="2" spans="1:3">
-      <x:c r="A2" s="2" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B2" s="2" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C2" s="2" t="s">
+      <x:c r="A2" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B2" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C2" s="3" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
-      <x:c r="A3" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B3" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C3" s="4" t="s">
+      <x:c r="A3" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B3" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C3" s="2" t="s">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:3">
+      <x:c r="A4" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B4" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C4" s="4" t="s">
         <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:3">
-      <x:c r="A4" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B4" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C4" s="3" t="s">
-        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
@@ -857,7 +857,7 @@
       <x:c r="B5" s="5" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C5" s="5" t="s"/>
+      <x:c r="C5" s="5"/>
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="6" t="s">
@@ -866,19 +866,19 @@
       <x:c r="B6" s="6" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C6" s="6" t="s"/>
+      <x:c r="C6" s="6"/>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="8" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B7" s="8" t="s"/>
+      <x:c r="B7" s="8"/>
       <x:c r="C7" s="8" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
-      <x:c r="A8" s="7" t="s"/>
+      <x:c r="A8" s="7"/>
       <x:c r="B8" s="7" t="s">
         <x:v>3</x:v>
       </x:c>
@@ -924,7 +924,7 @@
       </x:c>
     </x:row>
     <x:row r="5" spans="1:1">
-      <x:c r="A5" s="2" t="s">
+      <x:c r="A5" s="3" t="s">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -934,10 +934,10 @@
       </x:c>
     </x:row>
     <x:row r="7" spans="1:1">
-      <x:c r="A7" s="3" t="s"/>
+      <x:c r="A7" s="2"/>
     </x:row>
     <x:row r="8" spans="1:1">
-      <x:c r="A8" s="7" t="s"/>
+      <x:c r="A8" s="7"/>
     </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
@@ -967,7 +967,7 @@
       </x:c>
     </x:row>
     <x:row r="3" spans="1:1">
-      <x:c r="A3" s="2" t="s">
+      <x:c r="A3" s="3" t="s">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -987,10 +987,10 @@
       </x:c>
     </x:row>
     <x:row r="7" spans="1:1">
-      <x:c r="A7" s="7" t="s"/>
+      <x:c r="A7" s="2"/>
     </x:row>
     <x:row r="8" spans="1:1">
-      <x:c r="A8" s="3" t="s"/>
+      <x:c r="A8" s="7"/>
     </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
@@ -1011,24 +1011,24 @@
   <x:sheetData>
     <x:row r="1" spans="1:3">
       <x:c r="A1" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B2" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C2" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
@@ -1049,7 +1049,7 @@
       <x:c r="B4" s="5" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C4" s="5" t="s"/>
+      <x:c r="C4" s="5"/>
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
@@ -1069,19 +1069,19 @@
       <x:c r="B6" s="6" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C6" s="6" t="s"/>
+      <x:c r="C6" s="6"/>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="8" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B7" s="8" t="s"/>
+      <x:c r="B7" s="8"/>
       <x:c r="C7" s="8" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
-      <x:c r="A8" s="7" t="s"/>
+      <x:c r="A8" s="7"/>
       <x:c r="B8" s="7" t="s">
         <x:v>3</x:v>
       </x:c>
@@ -1113,13 +1113,13 @@
       <x:c r="B1" s="6" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C1" s="6" t="s"/>
+      <x:c r="C1" s="6"/>
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="8" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B2" s="8" t="s"/>
+      <x:c r="B2" s="8"/>
       <x:c r="C2" s="8" t="s">
         <x:v>5</x:v>
       </x:c>
@@ -1147,24 +1147,24 @@
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
-      <x:c r="A5" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B5" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C5" s="3" t="s">
+      <x:c r="A5" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B5" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C5" s="2" t="s">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
-      <x:c r="A6" s="2" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B6" s="2" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" s="2" t="s">
+      <x:c r="A6" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B6" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C6" s="3" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -1175,10 +1175,10 @@
       <x:c r="B7" s="5" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="5" t="s"/>
+      <x:c r="C7" s="5"/>
     </x:row>
     <x:row r="8" spans="1:3">
-      <x:c r="A8" s="7" t="s"/>
+      <x:c r="A8" s="7"/>
       <x:c r="B8" s="7" t="s">
         <x:v>3</x:v>
       </x:c>
@@ -1210,27 +1210,27 @@
       <x:c r="B1" s="6" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C1" s="6" t="s"/>
+      <x:c r="C1" s="6"/>
     </x:row>
     <x:row r="2" spans="1:3">
-      <x:c r="A2" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B2" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C2" s="3" t="s">
+      <x:c r="A2" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B2" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C2" s="2" t="s">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
-      <x:c r="A3" s="2" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B3" s="2" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C3" s="2" t="s">
+      <x:c r="A3" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B3" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C3" s="3" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -1252,10 +1252,10 @@
       <x:c r="B5" s="5" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C5" s="5" t="s"/>
+      <x:c r="C5" s="5"/>
     </x:row>
     <x:row r="6" spans="1:3">
-      <x:c r="A6" s="7" t="s"/>
+      <x:c r="A6" s="7"/>
       <x:c r="B6" s="7" t="s">
         <x:v>3</x:v>
       </x:c>
@@ -1278,7 +1278,7 @@
       <x:c r="A8" s="8" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B8" s="8" t="s"/>
+      <x:c r="B8" s="8"/>
       <x:c r="C8" s="8" t="s">
         <x:v>5</x:v>
       </x:c>
@@ -1301,13 +1301,13 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:1">
-      <x:c r="A1" s="1" t="s">
-        <x:v>3</x:v>
+      <x:c r="A1" s="5" t="s">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:1">
-      <x:c r="A2" s="5" t="s">
-        <x:v>5</x:v>
+      <x:c r="A2" s="1" t="s">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:1">
@@ -1321,7 +1321,7 @@
       </x:c>
     </x:row>
     <x:row r="5" spans="1:1">
-      <x:c r="A5" s="2" t="s">
+      <x:c r="A5" s="3" t="s">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -1331,10 +1331,10 @@
       </x:c>
     </x:row>
     <x:row r="7" spans="1:1">
-      <x:c r="A7" s="7" t="s"/>
+      <x:c r="A7" s="2"/>
     </x:row>
     <x:row r="8" spans="1:1">
-      <x:c r="A8" s="3" t="s"/>
+      <x:c r="A8" s="7"/>
     </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
@@ -1369,25 +1369,25 @@
       </x:c>
     </x:row>
     <x:row r="4" spans="1:1">
-      <x:c r="A4" s="2" t="s">
+      <x:c r="A4" s="3" t="s">
         <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:1">
-      <x:c r="A5" s="1" t="s">
-        <x:v>3</x:v>
+      <x:c r="A5" s="5" t="s">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:1">
-      <x:c r="A6" s="5" t="s">
-        <x:v>5</x:v>
+      <x:c r="A6" s="1" t="s">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:1">
-      <x:c r="A7" s="3" t="s"/>
+      <x:c r="A7" s="2"/>
     </x:row>
     <x:row r="8" spans="1:1">
-      <x:c r="A8" s="7" t="s"/>
+      <x:c r="A8" s="7"/>
     </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
@@ -1438,64 +1438,64 @@
       <x:c r="B3" s="5" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C3" s="5" t="s"/>
+      <x:c r="C3" s="5"/>
     </x:row>
     <x:row r="4" spans="1:3">
-      <x:c r="A4" s="6" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B4" s="6" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="6" t="s"/>
+      <x:c r="A4" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B4" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C4" s="2" t="s">
+        <x:v>3</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
-      <x:c r="A5" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B5" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C5" s="3" t="s">
-        <x:v>3</x:v>
+      <x:c r="A5" s="7"/>
+      <x:c r="B5" s="7" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C5" s="7" t="s">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
-      <x:c r="A6" s="7" t="s"/>
-      <x:c r="B6" s="7" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" s="7" t="s">
-        <x:v>5</x:v>
+      <x:c r="A6" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B6" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C6" s="4" t="s">
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
-      <x:c r="A7" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B7" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C7" s="4" t="s">
-        <x:v>6</x:v>
+      <x:c r="A7" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B7" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C7" s="3" t="s">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
-      <x:c r="A8" s="2" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B8" s="2" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C8" s="2" t="s">
-        <x:v>5</x:v>
-      </x:c>
+      <x:c r="A8" s="6" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B8" s="6" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C8" s="6"/>
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="8" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B9" s="8" t="s"/>
+      <x:c r="B9" s="8"/>
       <x:c r="C9" s="8" t="s">
         <x:v>5</x:v>
       </x:c>
@@ -1524,7 +1524,7 @@
       <x:c r="B1" s="8" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C1" s="8" t="s"/>
+      <x:c r="C1" s="8"/>
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="5" t="s">
@@ -1533,7 +1533,7 @@
       <x:c r="B2" s="5" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C2" s="5" t="s"/>
+      <x:c r="C2" s="5"/>
     </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
@@ -1556,42 +1556,42 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:2">
-      <x:c r="A1" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B1" s="6" t="s">
+      <x:c r="A1" s="5" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B1" s="5" t="s">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:2">
-      <x:c r="A2" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B2" s="5" t="s">
-        <x:v>3</x:v>
+      <x:c r="A2" s="1" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B2" s="2" t="s">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
-      <x:c r="A3" s="1" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B3" s="2" t="s">
+      <x:c r="A3" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B3" s="7" t="s">
         <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
-      <x:c r="A4" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B4" s="3" t="s">
+      <x:c r="A4" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B4" s="4" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
-      <x:c r="A5" s="2" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B5" s="7" t="s">
+      <x:c r="A5" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B5" s="3" t="s">
         <x:v>3</x:v>
       </x:c>
     </x:row>
@@ -1599,8 +1599,8 @@
       <x:c r="A6" s="8" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B6" s="4" t="s">
-        <x:v>5</x:v>
+      <x:c r="B6" s="6" t="s">
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:2">
@@ -1612,8 +1612,8 @@
       </x:c>
     </x:row>
     <x:row r="8" spans="1:2">
-      <x:c r="A8" s="7" t="s"/>
-      <x:c r="B8" s="8" t="s"/>
+      <x:c r="A8" s="7"/>
+      <x:c r="B8" s="8"/>
     </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
@@ -1663,10 +1663,10 @@
       </x:c>
     </x:row>
     <x:row r="7" spans="1:1">
-      <x:c r="A7" s="3" t="s"/>
+      <x:c r="A7" s="2"/>
     </x:row>
     <x:row r="8" spans="1:1">
-      <x:c r="A8" s="7" t="s"/>
+      <x:c r="A8" s="7"/>
     </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
@@ -1701,7 +1701,7 @@
       </x:c>
     </x:row>
     <x:row r="4" spans="1:1">
-      <x:c r="A4" s="2">
+      <x:c r="A4" s="3">
         <x:v>4.3</x:v>
       </x:c>
     </x:row>
@@ -1716,10 +1716,10 @@
       </x:c>
     </x:row>
     <x:row r="7" spans="1:1">
-      <x:c r="A7" s="7" t="s"/>
+      <x:c r="A7" s="2"/>
     </x:row>
     <x:row r="8" spans="1:1">
-      <x:c r="A8" s="3" t="s"/>
+      <x:c r="A8" s="7"/>
     </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
@@ -1769,10 +1769,10 @@
       </x:c>
     </x:row>
     <x:row r="7" spans="1:1">
-      <x:c r="A7" s="3" t="s"/>
+      <x:c r="A7" s="2"/>
     </x:row>
     <x:row r="8" spans="1:1">
-      <x:c r="A8" s="7" t="s"/>
+      <x:c r="A8" s="7"/>
     </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
@@ -1822,10 +1822,10 @@
       </x:c>
     </x:row>
     <x:row r="7" spans="1:1">
-      <x:c r="A7" s="7" t="s"/>
+      <x:c r="A7" s="2"/>
     </x:row>
     <x:row r="8" spans="1:1">
-      <x:c r="A8" s="3" t="s"/>
+      <x:c r="A8" s="7"/>
     </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
@@ -1845,7 +1845,7 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:3">
-      <x:c r="A1" s="7" t="s"/>
+      <x:c r="A1" s="7"/>
       <x:c r="B1" s="7" t="s">
         <x:v>3</x:v>
       </x:c>
@@ -1865,24 +1865,24 @@
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
-      <x:c r="A3" s="2" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B3" s="2" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C3" s="2" t="s">
+      <x:c r="A3" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B3" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C3" s="3" t="s">
         <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
-      <x:c r="A4" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B4" s="3" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C4" s="3" t="s">
+      <x:c r="A4" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B4" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C4" s="2" t="s">
         <x:v>3</x:v>
       </x:c>
     </x:row>
@@ -1904,7 +1904,7 @@
       <x:c r="B6" s="5" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C6" s="5" t="s"/>
+      <x:c r="C6" s="5"/>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="6" t="s">
@@ -1913,13 +1913,13 @@
       <x:c r="B7" s="6" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="s"/>
+      <x:c r="C7" s="6"/>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="8" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B8" s="8" t="s"/>
+      <x:c r="B8" s="8"/>
       <x:c r="C8" s="8" t="s">
         <x:v>5</x:v>
       </x:c>
